--- a/h100price/data/b300_rental_prices.xlsx
+++ b/h100price/data/b300_rental_prices.xlsx
@@ -18518,6 +18518,5704 @@
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G251">
+        <v>7.339259</v>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J251">
+        <v>1</v>
+      </c>
+      <c r="K251">
+        <v>7.339259</v>
+      </c>
+      <c r="L251">
+        <v>7.339259</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9645921,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G252">
+        <v>14.672593</v>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J252">
+        <v>2</v>
+      </c>
+      <c r="K252">
+        <v>7.336296</v>
+      </c>
+      <c r="L252">
+        <v>7.336296</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404975,"reliability":0.9645921,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G253">
+        <v>18.671111</v>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J253">
+        <v>2</v>
+      </c>
+      <c r="K253">
+        <v>9.335556</v>
+      </c>
+      <c r="L253">
+        <v>9.335556</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9837279,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G254">
+        <v>29.334815</v>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J254">
+        <v>4</v>
+      </c>
+      <c r="K254">
+        <v>7.333704</v>
+      </c>
+      <c r="L254">
+        <v>7.333704</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404991,"reliability":0.9020099,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G255">
+        <v>37.237037</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J255">
+        <v>4</v>
+      </c>
+      <c r="K255">
+        <v>9.309259</v>
+      </c>
+      <c r="L255">
+        <v>9.309259</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38260728,"reliability":0.9243507,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G256">
+        <v>37.334815</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J256">
+        <v>4</v>
+      </c>
+      <c r="K256">
+        <v>9.333704</v>
+      </c>
+      <c r="L256">
+        <v>9.333704</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.8682669,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G257">
+        <v>58.668148</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J257">
+        <v>8</v>
+      </c>
+      <c r="K257">
+        <v>7.333519</v>
+      </c>
+      <c r="L257">
+        <v>7.333519</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154050,"reliability":0.9643686,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G258">
+        <v>74.463704</v>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J258">
+        <v>8</v>
+      </c>
+      <c r="K258">
+        <v>9.307963</v>
+      </c>
+      <c r="L258">
+        <v>9.307963</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38260727,"reliability":0.9243507,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G259">
+        <v>74.668148</v>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J259">
+        <v>8</v>
+      </c>
+      <c r="K259">
+        <v>9.333519</v>
+      </c>
+      <c r="L259">
+        <v>9.333519</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8682669,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G260">
+        <v>7.339259</v>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J260">
+        <v>1</v>
+      </c>
+      <c r="K260">
+        <v>7.339259</v>
+      </c>
+      <c r="L260">
+        <v>7.339259</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404972,"reliability":0.9651111,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G261">
+        <v>14.668148</v>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J261">
+        <v>2</v>
+      </c>
+      <c r="K261">
+        <v>7.334074</v>
+      </c>
+      <c r="L261">
+        <v>7.334074</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154041,"reliability":0.9649963,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G262">
+        <v>18.671111</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J262">
+        <v>2</v>
+      </c>
+      <c r="K262">
+        <v>9.335556</v>
+      </c>
+      <c r="L262">
+        <v>9.335556</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9837972,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G263">
+        <v>29.334815</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J263">
+        <v>4</v>
+      </c>
+      <c r="K263">
+        <v>7.333704</v>
+      </c>
+      <c r="L263">
+        <v>7.333704</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154039,"reliability":0.9649963,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G264">
+        <v>37.237037</v>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J264">
+        <v>4</v>
+      </c>
+      <c r="K264">
+        <v>9.309259</v>
+      </c>
+      <c r="L264">
+        <v>9.309259</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38260728,"reliability":0.92532,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G265">
+        <v>37.334815</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J265">
+        <v>4</v>
+      </c>
+      <c r="K265">
+        <v>9.333704</v>
+      </c>
+      <c r="L265">
+        <v>9.333704</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.8727415,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G266">
+        <v>56.001481</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J266">
+        <v>8</v>
+      </c>
+      <c r="K266">
+        <v>7.000185</v>
+      </c>
+      <c r="L266">
+        <v>7.000185</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38268067,"reliability":0.9543217,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G267">
+        <v>74.463704</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J267">
+        <v>8</v>
+      </c>
+      <c r="K267">
+        <v>9.307963</v>
+      </c>
+      <c r="L267">
+        <v>9.307963</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38260727,"reliability":0.92532,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G268">
+        <v>74.668148</v>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J268">
+        <v>8</v>
+      </c>
+      <c r="K268">
+        <v>9.333519</v>
+      </c>
+      <c r="L268">
+        <v>9.333519</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8727415,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G269">
+        <v>7.334815</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J269">
+        <v>1</v>
+      </c>
+      <c r="K269">
+        <v>7.334815</v>
+      </c>
+      <c r="L269">
+        <v>7.334815</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154051,"reliability":0.9652959,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G270">
+        <v>14.668148</v>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J270">
+        <v>2</v>
+      </c>
+      <c r="K270">
+        <v>7.334074</v>
+      </c>
+      <c r="L270">
+        <v>7.334074</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404988,"reliability":0.9134983,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G271">
+        <v>18.671111</v>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J271">
+        <v>2</v>
+      </c>
+      <c r="K271">
+        <v>9.335556</v>
+      </c>
+      <c r="L271">
+        <v>9.335556</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9838746,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G272">
+        <v>29.334815</v>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J272">
+        <v>4</v>
+      </c>
+      <c r="K272">
+        <v>7.333704</v>
+      </c>
+      <c r="L272">
+        <v>7.333704</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154048,"reliability":0.9652959,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G273">
+        <v>37.237037</v>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J273">
+        <v>4</v>
+      </c>
+      <c r="K273">
+        <v>9.309259</v>
+      </c>
+      <c r="L273">
+        <v>9.309259</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38260728,"reliability":0.9263628,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G274">
+        <v>37.334815</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J274">
+        <v>4</v>
+      </c>
+      <c r="K274">
+        <v>9.333704</v>
+      </c>
+      <c r="L274">
+        <v>9.333704</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.877215,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G275">
+        <v>58.668148</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J275">
+        <v>8</v>
+      </c>
+      <c r="K275">
+        <v>7.333519</v>
+      </c>
+      <c r="L275">
+        <v>7.333519</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154050,"reliability":0.9652959,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G276">
+        <v>74.463704</v>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J276">
+        <v>8</v>
+      </c>
+      <c r="K276">
+        <v>9.307963</v>
+      </c>
+      <c r="L276">
+        <v>9.307963</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38260727,"reliability":0.9263628,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G277">
+        <v>74.668148</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J277">
+        <v>8</v>
+      </c>
+      <c r="K277">
+        <v>9.333519</v>
+      </c>
+      <c r="L277">
+        <v>9.333519</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.877215,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G278">
+        <v>7.339259</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J278">
+        <v>1</v>
+      </c>
+      <c r="K278">
+        <v>7.339259</v>
+      </c>
+      <c r="L278">
+        <v>7.339259</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.965183,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G279">
+        <v>14.668148</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J279">
+        <v>2</v>
+      </c>
+      <c r="K279">
+        <v>7.334074</v>
+      </c>
+      <c r="L279">
+        <v>7.334074</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154046,"reliability":0.9654443,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G280">
+        <v>17.21037</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J280">
+        <v>2</v>
+      </c>
+      <c r="K280">
+        <v>8.605185</v>
+      </c>
+      <c r="L280">
+        <v>8.605185</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456456,"reliability":0.9273214,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G281">
+        <v>18.671111</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J281">
+        <v>2</v>
+      </c>
+      <c r="K281">
+        <v>9.335556</v>
+      </c>
+      <c r="L281">
+        <v>9.335556</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9839488,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G282">
+        <v>32.001481</v>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J282">
+        <v>4</v>
+      </c>
+      <c r="K282">
+        <v>8.00037</v>
+      </c>
+      <c r="L282">
+        <v>8.00037</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404991,"reliability":0.9151004,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G283">
+        <v>34.41037</v>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J283">
+        <v>4</v>
+      </c>
+      <c r="K283">
+        <v>8.602593</v>
+      </c>
+      <c r="L283">
+        <v>8.602593</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456453,"reliability":0.9273214,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G284">
+        <v>37.334815</v>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J284">
+        <v>4</v>
+      </c>
+      <c r="K284">
+        <v>9.333704</v>
+      </c>
+      <c r="L284">
+        <v>9.333704</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.8811544,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G285">
+        <v>64.001481</v>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J285">
+        <v>8</v>
+      </c>
+      <c r="K285">
+        <v>8.000185</v>
+      </c>
+      <c r="L285">
+        <v>8.000185</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404992,"reliability":0.9151004,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G286">
+        <v>68.81037</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J286">
+        <v>8</v>
+      </c>
+      <c r="K286">
+        <v>8.601296</v>
+      </c>
+      <c r="L286">
+        <v>8.601296</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456458,"reliability":0.9273214,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G287">
+        <v>74.668148</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J287">
+        <v>8</v>
+      </c>
+      <c r="K287">
+        <v>9.333519</v>
+      </c>
+      <c r="L287">
+        <v>9.333519</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8811544,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G288">
+        <v>7.334815</v>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J288">
+        <v>1</v>
+      </c>
+      <c r="K288">
+        <v>7.334815</v>
+      </c>
+      <c r="L288">
+        <v>7.334815</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154051,"reliability":0.9654443,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G289">
+        <v>14.668148</v>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J289">
+        <v>2</v>
+      </c>
+      <c r="K289">
+        <v>7.334074</v>
+      </c>
+      <c r="L289">
+        <v>7.334074</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154041,"reliability":0.9654443,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G290">
+        <v>17.21037</v>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J290">
+        <v>2</v>
+      </c>
+      <c r="K290">
+        <v>8.605185</v>
+      </c>
+      <c r="L290">
+        <v>8.605185</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456455,"reliability":0.9273214,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G291">
+        <v>18.671111</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J291">
+        <v>2</v>
+      </c>
+      <c r="K291">
+        <v>9.335556</v>
+      </c>
+      <c r="L291">
+        <v>9.335556</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9839488,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G292">
+        <v>32.001481</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J292">
+        <v>4</v>
+      </c>
+      <c r="K292">
+        <v>8.00037</v>
+      </c>
+      <c r="L292">
+        <v>8.00037</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404987,"reliability":0.9151004,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G293">
+        <v>34.41037</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J293">
+        <v>4</v>
+      </c>
+      <c r="K293">
+        <v>8.602593</v>
+      </c>
+      <c r="L293">
+        <v>8.602593</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456457,"reliability":0.9273214,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G294">
+        <v>37.334815</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J294">
+        <v>4</v>
+      </c>
+      <c r="K294">
+        <v>9.333704</v>
+      </c>
+      <c r="L294">
+        <v>9.333704</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.8811544,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G295">
+        <v>64.001481</v>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J295">
+        <v>8</v>
+      </c>
+      <c r="K295">
+        <v>8.000185</v>
+      </c>
+      <c r="L295">
+        <v>8.000185</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404992,"reliability":0.9151004,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G296">
+        <v>68.81037</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J296">
+        <v>8</v>
+      </c>
+      <c r="K296">
+        <v>8.601296</v>
+      </c>
+      <c r="L296">
+        <v>8.601296</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456458,"reliability":0.9273214,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G297">
+        <v>74.668148</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J297">
+        <v>8</v>
+      </c>
+      <c r="K297">
+        <v>9.333519</v>
+      </c>
+      <c r="L297">
+        <v>9.333519</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8811544,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G298">
+        <v>7.339259</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J298">
+        <v>1</v>
+      </c>
+      <c r="K298">
+        <v>7.339259</v>
+      </c>
+      <c r="L298">
+        <v>7.339259</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9653552,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G299">
+        <v>9.335556</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J299">
+        <v>1</v>
+      </c>
+      <c r="K299">
+        <v>9.335556</v>
+      </c>
+      <c r="L299">
+        <v>9.335556</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345039,"reliability":0.9639402,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G300">
+        <v>14.668148</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J300">
+        <v>2</v>
+      </c>
+      <c r="K300">
+        <v>7.334074</v>
+      </c>
+      <c r="L300">
+        <v>7.334074</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154041,"reliability":0.9655646,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G301">
+        <v>17.21037</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J301">
+        <v>2</v>
+      </c>
+      <c r="K301">
+        <v>8.605185</v>
+      </c>
+      <c r="L301">
+        <v>8.605185</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456454,"reliability":0.9307482,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G302">
+        <v>18.668889</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J302">
+        <v>2</v>
+      </c>
+      <c r="K302">
+        <v>9.334444</v>
+      </c>
+      <c r="L302">
+        <v>9.334444</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345026,"reliability":0.9638508,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G303">
+        <v>18.671111</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J303">
+        <v>2</v>
+      </c>
+      <c r="K303">
+        <v>9.335556</v>
+      </c>
+      <c r="L303">
+        <v>9.335556</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9842316,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G304">
+        <v>29.334815</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J304">
+        <v>4</v>
+      </c>
+      <c r="K304">
+        <v>7.333704</v>
+      </c>
+      <c r="L304">
+        <v>7.333704</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154048,"reliability":0.9655646,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G305">
+        <v>34.41037</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J305">
+        <v>4</v>
+      </c>
+      <c r="K305">
+        <v>8.602593</v>
+      </c>
+      <c r="L305">
+        <v>8.602593</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456457,"reliability":0.9307482,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G306">
+        <v>37.334815</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J306">
+        <v>4</v>
+      </c>
+      <c r="K306">
+        <v>9.333704</v>
+      </c>
+      <c r="L306">
+        <v>9.333704</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294438,"reliability":0.8939438,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G307">
+        <v>37.335556</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J307">
+        <v>4</v>
+      </c>
+      <c r="K307">
+        <v>9.333889</v>
+      </c>
+      <c r="L307">
+        <v>9.333889</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345023,"reliability":0.9638508,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G308">
+        <v>61.334815</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J308">
+        <v>8</v>
+      </c>
+      <c r="K308">
+        <v>7.666852</v>
+      </c>
+      <c r="L308">
+        <v>7.666852</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38268067,"reliability":0.9551375,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G309">
+        <v>64.002222</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J309">
+        <v>8</v>
+      </c>
+      <c r="K309">
+        <v>8.000278</v>
+      </c>
+      <c r="L309">
+        <v>8.000278</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9599371,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G310">
+        <v>68.81037</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J310">
+        <v>8</v>
+      </c>
+      <c r="K310">
+        <v>8.601296</v>
+      </c>
+      <c r="L310">
+        <v>8.601296</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456458,"reliability":0.9307482,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G311">
+        <v>74.668148</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J311">
+        <v>8</v>
+      </c>
+      <c r="K311">
+        <v>9.333519</v>
+      </c>
+      <c r="L311">
+        <v>9.333519</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8939438,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G312">
+        <v>74.668889</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J312">
+        <v>8</v>
+      </c>
+      <c r="K312">
+        <v>9.333611</v>
+      </c>
+      <c r="L312">
+        <v>9.333611</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9638508,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G313">
+        <v>7.339259</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J313">
+        <v>1</v>
+      </c>
+      <c r="K313">
+        <v>7.339259</v>
+      </c>
+      <c r="L313">
+        <v>7.339259</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9653552,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G314">
+        <v>9.335556</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J314">
+        <v>1</v>
+      </c>
+      <c r="K314">
+        <v>9.335556</v>
+      </c>
+      <c r="L314">
+        <v>9.335556</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345020,"reliability":0.9638508,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G315">
+        <v>14.668148</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J315">
+        <v>2</v>
+      </c>
+      <c r="K315">
+        <v>7.334074</v>
+      </c>
+      <c r="L315">
+        <v>7.334074</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154037,"reliability":0.9655646,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G316">
+        <v>17.21037</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J316">
+        <v>2</v>
+      </c>
+      <c r="K316">
+        <v>8.605185</v>
+      </c>
+      <c r="L316">
+        <v>8.605185</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456456,"reliability":0.9307482,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G317">
+        <v>18.668889</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J317">
+        <v>2</v>
+      </c>
+      <c r="K317">
+        <v>9.334444</v>
+      </c>
+      <c r="L317">
+        <v>9.334444</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345021,"reliability":0.9638508,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G318">
+        <v>18.671111</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J318">
+        <v>2</v>
+      </c>
+      <c r="K318">
+        <v>9.335556</v>
+      </c>
+      <c r="L318">
+        <v>9.335556</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9842316,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G319">
+        <v>29.334815</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J319">
+        <v>4</v>
+      </c>
+      <c r="K319">
+        <v>7.333704</v>
+      </c>
+      <c r="L319">
+        <v>7.333704</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154048,"reliability":0.9655646,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G320">
+        <v>34.41037</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J320">
+        <v>4</v>
+      </c>
+      <c r="K320">
+        <v>8.602593</v>
+      </c>
+      <c r="L320">
+        <v>8.602593</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456453,"reliability":0.9307482,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G321">
+        <v>37.334815</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J321">
+        <v>4</v>
+      </c>
+      <c r="K321">
+        <v>9.333704</v>
+      </c>
+      <c r="L321">
+        <v>9.333704</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.8939438,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G322">
+        <v>37.335556</v>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J322">
+        <v>4</v>
+      </c>
+      <c r="K322">
+        <v>9.333889</v>
+      </c>
+      <c r="L322">
+        <v>9.333889</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345051,"reliability":0.9639402,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G323">
+        <v>61.334815</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J323">
+        <v>8</v>
+      </c>
+      <c r="K323">
+        <v>7.666852</v>
+      </c>
+      <c r="L323">
+        <v>7.666852</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38268067,"reliability":0.9551375,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G324">
+        <v>64.002222</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J324">
+        <v>8</v>
+      </c>
+      <c r="K324">
+        <v>8.000278</v>
+      </c>
+      <c r="L324">
+        <v>8.000278</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9599371,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G325">
+        <v>68.81037</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J325">
+        <v>8</v>
+      </c>
+      <c r="K325">
+        <v>8.601296</v>
+      </c>
+      <c r="L325">
+        <v>8.601296</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456458,"reliability":0.9307482,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G326">
+        <v>74.668148</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J326">
+        <v>8</v>
+      </c>
+      <c r="K326">
+        <v>9.333519</v>
+      </c>
+      <c r="L326">
+        <v>9.333519</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.8939438,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G327">
+        <v>74.668889</v>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J327">
+        <v>8</v>
+      </c>
+      <c r="K327">
+        <v>9.333611</v>
+      </c>
+      <c r="L327">
+        <v>9.333611</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.9638508,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/h100price/data/b300_rental_prices.xlsx
+++ b/h100price/data/b300_rental_prices.xlsx
@@ -45306,6 +45306,1412 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G613">
+        <v>7.339259</v>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J613">
+        <v>1</v>
+      </c>
+      <c r="K613">
+        <v>7.339259</v>
+      </c>
+      <c r="L613">
+        <v>7.339259</v>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38404965,"reliability":0.9657454,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G614">
+        <v>7.668148</v>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J614">
+        <v>1</v>
+      </c>
+      <c r="K614">
+        <v>7.668148</v>
+      </c>
+      <c r="L614">
+        <v>7.668148</v>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487077,"reliability":0.9192806,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x1</t>
+        </is>
+      </c>
+      <c r="G615">
+        <v>9.335556</v>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J615">
+        <v>1</v>
+      </c>
+      <c r="K615">
+        <v>9.335556</v>
+      </c>
+      <c r="L615">
+        <v>9.335556</v>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345028,"reliability":0.964355,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G616">
+        <v>14.668148</v>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J616">
+        <v>2</v>
+      </c>
+      <c r="K616">
+        <v>7.334074</v>
+      </c>
+      <c r="L616">
+        <v>7.334074</v>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38154041,"reliability":0.9658661,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G617">
+        <v>15.334815</v>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J617">
+        <v>2</v>
+      </c>
+      <c r="K617">
+        <v>7.667407</v>
+      </c>
+      <c r="L617">
+        <v>7.667407</v>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487075,"reliability":0.9192806,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G618">
+        <v>17.877037</v>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J618">
+        <v>2</v>
+      </c>
+      <c r="K618">
+        <v>8.938519</v>
+      </c>
+      <c r="L618">
+        <v>8.938519</v>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456452,"reliability":0.9390298,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G619">
+        <v>18.668889</v>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J619">
+        <v>2</v>
+      </c>
+      <c r="K619">
+        <v>9.334444</v>
+      </c>
+      <c r="L619">
+        <v>9.334444</v>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345045,"reliability":0.9643525,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G620">
+        <v>18.668889</v>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J620">
+        <v>2</v>
+      </c>
+      <c r="K620">
+        <v>9.334444</v>
+      </c>
+      <c r="L620">
+        <v>9.334444</v>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345026,"reliability":0.964355,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x2</t>
+        </is>
+      </c>
+      <c r="G621">
+        <v>18.671111</v>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J621">
+        <v>2</v>
+      </c>
+      <c r="K621">
+        <v>9.335556</v>
+      </c>
+      <c r="L621">
+        <v>9.335556</v>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37430320,"reliability":0.9850868,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G622">
+        <v>30.668148</v>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J622">
+        <v>4</v>
+      </c>
+      <c r="K622">
+        <v>7.667037</v>
+      </c>
+      <c r="L622">
+        <v>7.667037</v>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487081,"reliability":0.9192806,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G623">
+        <v>34.668148</v>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J623">
+        <v>4</v>
+      </c>
+      <c r="K623">
+        <v>8.667037</v>
+      </c>
+      <c r="L623">
+        <v>8.667037</v>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294439,"reliability":0.9184775,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G624">
+        <v>35.743704</v>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J624">
+        <v>4</v>
+      </c>
+      <c r="K624">
+        <v>8.935926</v>
+      </c>
+      <c r="L624">
+        <v>8.935926</v>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456453,"reliability":0.9390298,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x4</t>
+        </is>
+      </c>
+      <c r="G625">
+        <v>37.335556</v>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J625">
+        <v>4</v>
+      </c>
+      <c r="K625">
+        <v>9.333889</v>
+      </c>
+      <c r="L625">
+        <v>9.333889</v>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345042,"reliability":0.9643525,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G626">
+        <v>58.668148</v>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J626">
+        <v>8</v>
+      </c>
+      <c r="K626">
+        <v>7.333519</v>
+      </c>
+      <c r="L626">
+        <v>7.333519</v>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38529450,"reliability":0.9650879,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G627">
+        <v>61.334815</v>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J627">
+        <v>8</v>
+      </c>
+      <c r="K627">
+        <v>7.666852</v>
+      </c>
+      <c r="L627">
+        <v>7.666852</v>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38487082,"reliability":0.9192806,"location":", CA"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G628">
+        <v>64.002222</v>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J628">
+        <v>8</v>
+      </c>
+      <c r="K628">
+        <v>8.000278</v>
+      </c>
+      <c r="L628">
+        <v>8.000278</v>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474247,"reliability":0.9608315,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G629">
+        <v>69.334815</v>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J629">
+        <v>8</v>
+      </c>
+      <c r="K629">
+        <v>8.666852</v>
+      </c>
+      <c r="L629">
+        <v>8.666852</v>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38294437,"reliability":0.9184775,"location":"Taiwan, TW"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G630">
+        <v>74.668889</v>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J630">
+        <v>8</v>
+      </c>
+      <c r="K630">
+        <v>9.333611</v>
+      </c>
+      <c r="L630">
+        <v>9.333611</v>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345052,"reliability":0.9643525,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:29Z</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>B300 SXM6 AC x8</t>
+        </is>
+      </c>
+      <c r="G631">
+        <v>74.668889</v>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J631">
+        <v>8</v>
+      </c>
+      <c r="K631">
+        <v>9.333611</v>
+      </c>
+      <c r="L631">
+        <v>9.333611</v>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38345033,"reliability":0.964355,"location":"Utah, US"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>